--- a/outputs/scenario_campaigns_20260716/04_pause_staging_artifact.xlsx
+++ b/outputs/scenario_campaigns_20260716/04_pause_staging_artifact.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R5b7bbddf45a64161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R2042bc9f0c074e8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -713,15 +713,15 @@
       </x:c>
       <x:c r="D14"/>
       <x:c r="E14" t="str">
-        <x:v>Drone Detection System 南美 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F14"/>
       <x:c r="G14" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>UAV Detection Systems</x:v>
       </x:c>
       <x:c r="H14"/>
       <x:c r="I14" t="str">
-        <x:v>enterprise drone detection system</x:v>
+        <x:v>uav mine detection</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>Exact match</x:v>
@@ -751,11 +751,11 @@
       </x:c>
       <x:c r="F15"/>
       <x:c r="G15" t="str">
-        <x:v>UAV Detection Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H15"/>
       <x:c r="I15" t="str">
-        <x:v>uav airport detection</x:v>
+        <x:v>enterprise drone detection system</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Exact match</x:v>
@@ -781,15 +781,15 @@
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 南美 精准</x:v>
       </x:c>
       <x:c r="F16"/>
       <x:c r="G16" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>UAV Detection Systems</x:v>
       </x:c>
       <x:c r="H16"/>
       <x:c r="I16" t="str">
-        <x:v>airport anti drone systems</x:v>
+        <x:v>uav airport detection</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Exact match</x:v>
@@ -815,15 +815,15 @@
       </x:c>
       <x:c r="D17"/>
       <x:c r="E17" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 南美 精准</x:v>
       </x:c>
       <x:c r="F17"/>
       <x:c r="G17" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>UAV Detection Systems</x:v>
       </x:c>
       <x:c r="H17"/>
       <x:c r="I17" t="str">
-        <x:v>law enforcement anti drone systems</x:v>
+        <x:v>uav mine detection</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Exact match</x:v>
@@ -849,7 +849,7 @@
       </x:c>
       <x:c r="D18"/>
       <x:c r="E18" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F18"/>
       <x:c r="G18" t="str">
@@ -857,7 +857,7 @@
       </x:c>
       <x:c r="H18"/>
       <x:c r="I18" t="str">
-        <x:v>anti drone system for prison</x:v>
+        <x:v>airport anti drone systems</x:v>
       </x:c>
       <x:c r="J18" t="str">
         <x:v>Exact match</x:v>
@@ -883,15 +883,15 @@
       </x:c>
       <x:c r="D19"/>
       <x:c r="E19" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F19"/>
       <x:c r="G19" t="str">
-        <x:v>UAV Detection Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H19"/>
       <x:c r="I19" t="str">
-        <x:v>uav airport detection</x:v>
+        <x:v>law enforcement anti drone systems</x:v>
       </x:c>
       <x:c r="J19" t="str">
         <x:v>Exact match</x:v>
@@ -917,7 +917,7 @@
       </x:c>
       <x:c r="D20"/>
       <x:c r="E20" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F20"/>
       <x:c r="G20" t="str">
@@ -951,15 +951,15 @@
       </x:c>
       <x:c r="D21"/>
       <x:c r="E21" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F21"/>
       <x:c r="G21" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>UAV Detection Systems</x:v>
       </x:c>
       <x:c r="H21"/>
       <x:c r="I21" t="str">
-        <x:v>anti drone system airport</x:v>
+        <x:v>uav airport detection</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Exact match</x:v>
@@ -993,7 +993,7 @@
       </x:c>
       <x:c r="H22"/>
       <x:c r="I22" t="str">
-        <x:v>airport anti drone system</x:v>
+        <x:v>anti drone system for prison</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>Exact match</x:v>
@@ -1019,15 +1019,15 @@
       </x:c>
       <x:c r="D23"/>
       <x:c r="E23" t="str">
-        <x:v>Drone Detection System 南美 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F23"/>
       <x:c r="G23" t="str">
-        <x:v>Drone Detection Radar</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>airport anti drone detection radar</x:v>
+        <x:v>anti drone system airport</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Exact match</x:v>
@@ -1053,15 +1053,15 @@
       </x:c>
       <x:c r="D24"/>
       <x:c r="E24" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F24"/>
       <x:c r="G24" t="str">
-        <x:v>Counter Drone Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>police counter drone equipment</x:v>
+        <x:v>airport anti drone system</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>Exact match</x:v>
@@ -1087,15 +1087,15 @@
       </x:c>
       <x:c r="D25"/>
       <x:c r="E25" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Drone Detection System 南美 精准</x:v>
       </x:c>
       <x:c r="F25"/>
       <x:c r="G25" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Detection Radar</x:v>
       </x:c>
       <x:c r="H25"/>
       <x:c r="I25" t="str">
-        <x:v>anti drone system for police</x:v>
+        <x:v>airport anti drone detection radar</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Exact match</x:v>
@@ -1121,15 +1121,15 @@
       </x:c>
       <x:c r="D26"/>
       <x:c r="E26" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F26"/>
       <x:c r="G26" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Counter Drone Systems</x:v>
       </x:c>
       <x:c r="H26"/>
       <x:c r="I26" t="str">
-        <x:v>critical infrastructure drone detection system</x:v>
+        <x:v>police counter drone equipment</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>Exact match</x:v>
@@ -1159,11 +1159,11 @@
       </x:c>
       <x:c r="F27"/>
       <x:c r="G27" t="str">
-        <x:v>Counter Drone Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>prison counter drone</x:v>
+        <x:v>anti drone system for police</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>Exact match</x:v>
@@ -1189,15 +1189,15 @@
       </x:c>
       <x:c r="D28"/>
       <x:c r="E28" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Drone Detection System 中东 精准</x:v>
       </x:c>
       <x:c r="F28"/>
       <x:c r="G28" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H28"/>
       <x:c r="I28" t="str">
-        <x:v>airport drone defense</x:v>
+        <x:v>critical infrastructure drone detection system</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>Exact match</x:v>
@@ -1223,15 +1223,15 @@
       </x:c>
       <x:c r="D29"/>
       <x:c r="E29" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F29"/>
       <x:c r="G29" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Counter Drone Systems</x:v>
       </x:c>
       <x:c r="H29"/>
       <x:c r="I29" t="str">
-        <x:v>stadium drone detection system</x:v>
+        <x:v>prison counter drone</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>Exact match</x:v>
@@ -1257,15 +1257,15 @@
       </x:c>
       <x:c r="D30"/>
       <x:c r="E30" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F30"/>
       <x:c r="G30" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>enterprise drone detection system</x:v>
+        <x:v>airport drone defense</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>Exact match</x:v>
@@ -1291,15 +1291,15 @@
       </x:c>
       <x:c r="D31"/>
       <x:c r="E31" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F31"/>
       <x:c r="G31" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H31"/>
       <x:c r="I31" t="str">
-        <x:v>urban drone defense systems</x:v>
+        <x:v>stadium drone detection system</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>Exact match</x:v>
@@ -1325,15 +1325,15 @@
       </x:c>
       <x:c r="D32"/>
       <x:c r="E32" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F32"/>
       <x:c r="G32" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H32"/>
       <x:c r="I32" t="str">
-        <x:v>urban drone defense systems</x:v>
+        <x:v>enterprise drone detection system</x:v>
       </x:c>
       <x:c r="J32" t="str">
         <x:v>Exact match</x:v>
@@ -1359,15 +1359,15 @@
       </x:c>
       <x:c r="D33"/>
       <x:c r="E33" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F33"/>
       <x:c r="G33" t="str">
-        <x:v>Counter Drone Systems</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H33"/>
       <x:c r="I33" t="str">
-        <x:v>prison counter drone</x:v>
+        <x:v>urban drone defense systems</x:v>
       </x:c>
       <x:c r="J33" t="str">
         <x:v>Exact match</x:v>
@@ -1393,7 +1393,7 @@
       </x:c>
       <x:c r="D34"/>
       <x:c r="E34" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F34"/>
       <x:c r="G34" t="str">
@@ -1401,7 +1401,7 @@
       </x:c>
       <x:c r="H34"/>
       <x:c r="I34" t="str">
-        <x:v>airport defense against drones</x:v>
+        <x:v>urban drone defense systems</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Exact match</x:v>
@@ -1427,15 +1427,15 @@
       </x:c>
       <x:c r="D35"/>
       <x:c r="E35" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F35"/>
       <x:c r="G35" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Counter Drone Systems</x:v>
       </x:c>
       <x:c r="H35"/>
       <x:c r="I35" t="str">
-        <x:v>enterprise drone detection system</x:v>
+        <x:v>prison counter drone</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Exact match</x:v>
@@ -1461,15 +1461,15 @@
       </x:c>
       <x:c r="D36"/>
       <x:c r="E36" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F36"/>
       <x:c r="G36" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:v>stadium drone detection system</x:v>
+        <x:v>airport defense against drones</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Exact match</x:v>
@@ -1495,15 +1495,15 @@
       </x:c>
       <x:c r="D37"/>
       <x:c r="E37" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Drone Detection System 中东 精准</x:v>
       </x:c>
       <x:c r="F37"/>
       <x:c r="G37" t="str">
-        <x:v>Drone Detection Radar</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H37"/>
       <x:c r="I37" t="str">
-        <x:v>critical infrastructure drone radar</x:v>
+        <x:v>enterprise drone detection system</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Exact match</x:v>
@@ -1529,15 +1529,15 @@
       </x:c>
       <x:c r="D38"/>
       <x:c r="E38" t="str">
-        <x:v>Anti Drone  英语区 精准</x:v>
+        <x:v>Drone Detection System 中东 精准</x:v>
       </x:c>
       <x:c r="F38"/>
       <x:c r="G38" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H38"/>
       <x:c r="I38" t="str">
-        <x:v>airport defense against drones</x:v>
+        <x:v>stadium drone detection system</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Exact match</x:v>
@@ -1571,7 +1571,7 @@
       </x:c>
       <x:c r="H39"/>
       <x:c r="I39" t="str">
-        <x:v>airport anti drone detection radar</x:v>
+        <x:v>critical infrastructure drone radar</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Exact match</x:v>
@@ -1597,15 +1597,15 @@
       </x:c>
       <x:c r="D40"/>
       <x:c r="E40" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Anti Drone  英语区 精准</x:v>
       </x:c>
       <x:c r="F40"/>
       <x:c r="G40" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H40"/>
       <x:c r="I40" t="str">
-        <x:v>anti drone system for stadium</x:v>
+        <x:v>airport defense against drones</x:v>
       </x:c>
       <x:c r="J40" t="str">
         <x:v>Exact match</x:v>
@@ -1631,15 +1631,15 @@
       </x:c>
       <x:c r="D41"/>
       <x:c r="E41" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F41"/>
       <x:c r="G41" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Detection Radar</x:v>
       </x:c>
       <x:c r="H41"/>
       <x:c r="I41" t="str">
-        <x:v>anti drone system for police</x:v>
+        <x:v>airport anti drone detection radar</x:v>
       </x:c>
       <x:c r="J41" t="str">
         <x:v>Exact match</x:v>
@@ -1665,15 +1665,15 @@
       </x:c>
       <x:c r="D42"/>
       <x:c r="E42" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F42"/>
       <x:c r="G42" t="str">
-        <x:v>Drone Detection System</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H42"/>
       <x:c r="I42" t="str">
-        <x:v>critical infrastructure drone detection system</x:v>
+        <x:v>anti drone system for stadium</x:v>
       </x:c>
       <x:c r="J42" t="str">
         <x:v>Exact match</x:v>
@@ -1699,15 +1699,15 @@
       </x:c>
       <x:c r="D43"/>
       <x:c r="E43" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F43"/>
       <x:c r="G43" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H43"/>
       <x:c r="I43" t="str">
-        <x:v>airport drone defense</x:v>
+        <x:v>anti drone system for police</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Exact match</x:v>
@@ -1733,15 +1733,15 @@
       </x:c>
       <x:c r="D44"/>
       <x:c r="E44" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F44"/>
       <x:c r="G44" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Detection System</x:v>
       </x:c>
       <x:c r="H44"/>
       <x:c r="I44" t="str">
-        <x:v>anti drone airport</x:v>
+        <x:v>critical infrastructure drone detection system</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Exact match</x:v>
@@ -1767,15 +1767,15 @@
       </x:c>
       <x:c r="D45"/>
       <x:c r="E45" t="str">
-        <x:v>Drone Detection System 英语区 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F45"/>
       <x:c r="G45" t="str">
-        <x:v>Drone Detection Radar</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H45"/>
       <x:c r="I45" t="str">
-        <x:v>airport drone detection radar</x:v>
+        <x:v>airport drone defense</x:v>
       </x:c>
       <x:c r="J45" t="str">
         <x:v>Exact match</x:v>
@@ -1801,7 +1801,7 @@
       </x:c>
       <x:c r="D46"/>
       <x:c r="E46" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F46"/>
       <x:c r="G46" t="str">
@@ -1809,7 +1809,7 @@
       </x:c>
       <x:c r="H46"/>
       <x:c r="I46" t="str">
-        <x:v>anti drone system for prison</x:v>
+        <x:v>anti drone airport</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>Exact match</x:v>
@@ -1835,15 +1835,15 @@
       </x:c>
       <x:c r="D47"/>
       <x:c r="E47" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Drone Detection System 英语区 精准</x:v>
       </x:c>
       <x:c r="F47"/>
       <x:c r="G47" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Drone Detection Radar</x:v>
       </x:c>
       <x:c r="H47"/>
       <x:c r="I47" t="str">
-        <x:v>urban drone defense systems</x:v>
+        <x:v>airport drone detection radar</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Exact match</x:v>
@@ -1869,15 +1869,15 @@
       </x:c>
       <x:c r="D48"/>
       <x:c r="E48" t="str">
-        <x:v>Anti Drone  中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F48"/>
       <x:c r="G48" t="str">
-        <x:v>Drone Defense Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H48"/>
       <x:c r="I48" t="str">
-        <x:v>airport defense against drones</x:v>
+        <x:v>anti drone system for prison</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Exact match</x:v>
@@ -1907,11 +1907,11 @@
       </x:c>
       <x:c r="F49"/>
       <x:c r="G49" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H49"/>
       <x:c r="I49" t="str">
-        <x:v>anti drone system for airport</x:v>
+        <x:v>urban drone defense systems</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Exact match</x:v>
@@ -1945,7 +1945,7 @@
       </x:c>
       <x:c r="H50"/>
       <x:c r="I50" t="str">
-        <x:v>airport drone defense</x:v>
+        <x:v>airport defense against drones</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Exact match</x:v>
@@ -1971,7 +1971,7 @@
       </x:c>
       <x:c r="D51"/>
       <x:c r="E51" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F51"/>
       <x:c r="G51" t="str">
@@ -1979,7 +1979,7 @@
       </x:c>
       <x:c r="H51"/>
       <x:c r="I51" t="str">
-        <x:v>airport anti drone systems</x:v>
+        <x:v>anti drone system for airport</x:v>
       </x:c>
       <x:c r="J51" t="str">
         <x:v>Exact match</x:v>
@@ -2005,15 +2005,15 @@
       </x:c>
       <x:c r="D52"/>
       <x:c r="E52" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Anti Drone  中东 精准</x:v>
       </x:c>
       <x:c r="F52"/>
       <x:c r="G52" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Defense Systems</x:v>
       </x:c>
       <x:c r="H52"/>
       <x:c r="I52" t="str">
-        <x:v>anti drone system for police</x:v>
+        <x:v>airport drone defense</x:v>
       </x:c>
       <x:c r="J52" t="str">
         <x:v>Exact match</x:v>
@@ -2047,7 +2047,7 @@
       </x:c>
       <x:c r="H53"/>
       <x:c r="I53" t="str">
-        <x:v>anti drone system for stadium</x:v>
+        <x:v>airport anti drone systems</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Exact match</x:v>
@@ -2081,7 +2081,7 @@
       </x:c>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:v>airport anti drone system</x:v>
+        <x:v>anti drone system for police</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Exact match</x:v>
@@ -2107,15 +2107,15 @@
       </x:c>
       <x:c r="D55"/>
       <x:c r="E55" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F55"/>
       <x:c r="G55" t="str">
-        <x:v>Drone Detection Radar</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H55"/>
       <x:c r="I55" t="str">
-        <x:v>critical infrastructure drone radar</x:v>
+        <x:v>anti drone system for stadium</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Exact match</x:v>
@@ -2145,11 +2145,11 @@
       </x:c>
       <x:c r="F56"/>
       <x:c r="G56" t="str">
-        <x:v>Counter Drone Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H56"/>
       <x:c r="I56" t="str">
-        <x:v>prison counter drone</x:v>
+        <x:v>airport anti drone system</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Exact match</x:v>
@@ -2183,7 +2183,7 @@
       </x:c>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:v>airport anti drone detection radar</x:v>
+        <x:v>critical infrastructure drone radar</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Exact match</x:v>
@@ -2217,7 +2217,7 @@
       </x:c>
       <x:c r="H58"/>
       <x:c r="I58" t="str">
-        <x:v>police counter drone equipment</x:v>
+        <x:v>prison counter drone</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Exact match</x:v>
@@ -2243,15 +2243,15 @@
       </x:c>
       <x:c r="D59"/>
       <x:c r="E59" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Drone Detection System 中东 精准</x:v>
       </x:c>
       <x:c r="F59"/>
       <x:c r="G59" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Detection Radar</x:v>
       </x:c>
       <x:c r="H59"/>
       <x:c r="I59" t="str">
-        <x:v>law enforcement anti drone systems</x:v>
+        <x:v>airport anti drone detection radar</x:v>
       </x:c>
       <x:c r="J59" t="str">
         <x:v>Exact match</x:v>
@@ -2281,11 +2281,11 @@
       </x:c>
       <x:c r="F60"/>
       <x:c r="G60" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Counter Drone Systems</x:v>
       </x:c>
       <x:c r="H60"/>
       <x:c r="I60" t="str">
-        <x:v>anti drone airport</x:v>
+        <x:v>police counter drone equipment</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>Exact match</x:v>
@@ -2319,7 +2319,7 @@
       </x:c>
       <x:c r="H61"/>
       <x:c r="I61" t="str">
-        <x:v>anti drone system airport</x:v>
+        <x:v>law enforcement anti drone systems</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>Exact match</x:v>
@@ -2345,15 +2345,15 @@
       </x:c>
       <x:c r="D62"/>
       <x:c r="E62" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F62"/>
       <x:c r="G62" t="str">
-        <x:v>Drone Detection Radar</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H62"/>
       <x:c r="I62" t="str">
-        <x:v>airport drone detection radar</x:v>
+        <x:v>anti drone airport</x:v>
       </x:c>
       <x:c r="J62" t="str">
         <x:v>Exact match</x:v>
@@ -2379,15 +2379,15 @@
       </x:c>
       <x:c r="D63"/>
       <x:c r="E63" t="str">
-        <x:v>Drone Detection System 中东 精准</x:v>
+        <x:v>Anti Drone  南美 精准</x:v>
       </x:c>
       <x:c r="F63"/>
       <x:c r="G63" t="str">
-        <x:v>UAV Detection Systems</x:v>
+        <x:v>Anti Drone Systems</x:v>
       </x:c>
       <x:c r="H63"/>
       <x:c r="I63" t="str">
-        <x:v>uav airport detection</x:v>
+        <x:v>anti drone system airport</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>Exact match</x:v>
@@ -2413,15 +2413,15 @@
       </x:c>
       <x:c r="D64"/>
       <x:c r="E64" t="str">
-        <x:v>Anti Drone  南美 精准</x:v>
+        <x:v>Drone Detection System 中东 精准</x:v>
       </x:c>
       <x:c r="F64"/>
       <x:c r="G64" t="str">
-        <x:v>Anti Drone Systems</x:v>
+        <x:v>Drone Detection Radar</x:v>
       </x:c>
       <x:c r="H64"/>
       <x:c r="I64" t="str">
-        <x:v>anti drone system for airport</x:v>
+        <x:v>airport drone detection radar</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>Exact match</x:v>
@@ -2435,6 +2435,108 @@
       <x:c r="Q64"/>
       <x:c r="R64"/>
     </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>Keyword</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>Edit</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Paused</x:v>
+      </x:c>
+      <x:c r="D65"/>
+      <x:c r="E65" t="str">
+        <x:v>Drone Detection System 中东 精准</x:v>
+      </x:c>
+      <x:c r="F65"/>
+      <x:c r="G65" t="str">
+        <x:v>UAV Detection Systems</x:v>
+      </x:c>
+      <x:c r="H65"/>
+      <x:c r="I65" t="str">
+        <x:v>uav mine detection</x:v>
+      </x:c>
+      <x:c r="J65" t="str">
+        <x:v>Exact match</x:v>
+      </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
+      <x:c r="O65"/>
+      <x:c r="P65"/>
+      <x:c r="Q65"/>
+      <x:c r="R65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>Keyword</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Edit</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Paused</x:v>
+      </x:c>
+      <x:c r="D66"/>
+      <x:c r="E66" t="str">
+        <x:v>Drone Detection System 中东 精准</x:v>
+      </x:c>
+      <x:c r="F66"/>
+      <x:c r="G66" t="str">
+        <x:v>UAV Detection Systems</x:v>
+      </x:c>
+      <x:c r="H66"/>
+      <x:c r="I66" t="str">
+        <x:v>uav airport detection</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>Exact match</x:v>
+      </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+      <x:c r="P66"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>Keyword</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Edit</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Paused</x:v>
+      </x:c>
+      <x:c r="D67"/>
+      <x:c r="E67" t="str">
+        <x:v>Anti Drone  南美 精准</x:v>
+      </x:c>
+      <x:c r="F67"/>
+      <x:c r="G67" t="str">
+        <x:v>Anti Drone Systems</x:v>
+      </x:c>
+      <x:c r="H67"/>
+      <x:c r="I67" t="str">
+        <x:v>anti drone system for airport</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>Exact match</x:v>
+      </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
+      <x:c r="P67"/>
+      <x:c r="Q67"/>
+      <x:c r="R67"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
